--- a/artfynd/A 2194-2025 artfynd.xlsx
+++ b/artfynd/A 2194-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13460146</v>
+        <v>18450</v>
       </c>
       <c r="B2" t="n">
-        <v>59187</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101268</v>
+        <v>100077</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Margaritifera margaritifera</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,22 +703,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tormestorpsån: Sandåkra, Sk</t>
+          <t>Tormestorpsån Råbockamölla, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421617.0181917302</v>
+        <v>421611</v>
       </c>
       <c r="R2" t="n">
-        <v>6215717.37259012</v>
+        <v>6215767</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-06-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-02-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även spillning. Observatör Bengt Göran Andersson.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,145 +774,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Sundström</t>
+          <t>Anders Hallengren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Sundström</t>
+          <t>Via Anders Hallengren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering Unio crassus Hässleholms kommun</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>18450</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57434</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tormestorpsån Råbockamölla, Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>421611.2053124497</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6215766.587929083</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hässleholm</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Norra Mellby</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2010-02-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2010-02-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Även spillning. Observatör Bengt Göran Andersson.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Anders Hallengren</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Anders Hallengren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>

--- a/artfynd/A 2194-2025 artfynd.xlsx
+++ b/artfynd/A 2194-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,8 +792,16 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/18450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>